--- a/measurements/26/Filled_2D_sections/axial/week26_axial_Batch_Allmarks.xlsx
+++ b/measurements/26/Filled_2D_sections/axial/week26_axial_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,62 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,17 +556,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6.592801903628793</v>
+        <v>2513.038548752834</v>
       </c>
       <c r="D2" t="n">
-        <v>15.31006743849778</v>
+        <v>298.910840465909</v>
       </c>
       <c r="E2" t="n">
-        <v>11.02169243882342</v>
+        <v>215.1854238056001</v>
       </c>
       <c r="F2" t="n">
         <v>1.389084981592187</v>
@@ -525,24 +575,48 @@
         <v>0.3534481258339988</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>1.441215701219512</v>
+        <v>3.809523809523809</v>
       </c>
       <c r="J2" t="n">
-        <v>1.441215701219512</v>
+        <v>28.13802083333333</v>
       </c>
       <c r="K2" t="n">
-        <v>1.441215701219512</v>
-      </c>
-      <c r="N2" t="inlineStr">
+        <v>10.90727306547619</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>28.13802083333333</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O2" t="n">
+        <v>6.0546875</v>
+      </c>
+      <c r="P2" t="n">
+        <v>5.626860119047619</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>6.624895895300416</v>
+      <c r="Y2" s="2" t="n">
+        <v>2525.272108843537</v>
       </c>
     </row>
     <row r="3">
@@ -553,17 +627,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6.635633551457466</v>
+        <v>2529.365079365079</v>
       </c>
       <c r="D3" t="n">
-        <v>15.31006740069971</v>
+        <v>298.9108397279467</v>
       </c>
       <c r="E3" t="n">
-        <v>11.07047291209058</v>
+        <v>216.1378044741494</v>
       </c>
       <c r="F3" t="n">
         <v>1.382964171655112</v>
@@ -572,24 +646,48 @@
         <v>0.3557443843069981</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>1.415396341463415</v>
+        <v>3.627232142857143</v>
       </c>
       <c r="J3" t="n">
-        <v>1.415396341463415</v>
+        <v>27.63392857142857</v>
       </c>
       <c r="K3" t="n">
-        <v>1.415396341463415</v>
-      </c>
-      <c r="N3" t="inlineStr">
+        <v>10.84216889880952</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>27.63392857142857</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O3" t="n">
+        <v>6.0546875</v>
+      </c>
+      <c r="P3" t="n">
+        <v>6.05282738095238</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.627232142857143</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>12.93093870398475</v>
+      <c r="Y3" s="2" t="n">
+        <v>252.4611842206546</v>
       </c>
     </row>
     <row r="4">
@@ -600,17 +698,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6.681142177275432</v>
+        <v>2546.712018140589</v>
       </c>
       <c r="D4" t="n">
-        <v>15.36129923273877</v>
+        <v>299.9110802582332</v>
       </c>
       <c r="E4" t="n">
-        <v>11.10741728398858</v>
+        <v>216.8590993540627</v>
       </c>
       <c r="F4" t="n">
         <v>1.382976693860435</v>
@@ -619,24 +717,48 @@
         <v>0.3557989642889953</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>1.414634146341464</v>
+        <v>3.809523809523809</v>
       </c>
       <c r="J4" t="n">
-        <v>1.414634146341464</v>
+        <v>27.61904761904762</v>
       </c>
       <c r="K4" t="n">
-        <v>1.414634146341464</v>
-      </c>
-      <c r="N4" t="inlineStr">
+        <v>10.91006324404762</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>27.61904761904762</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O4" t="n">
+        <v>6.134672619047619</v>
+      </c>
+      <c r="P4" t="n">
+        <v>6.077008928571428</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>10.79406828487792</v>
+      <c r="Y4" s="2" t="n">
+        <v>210.7413331809498</v>
       </c>
     </row>
     <row r="5">
@@ -647,42 +769,66 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6.718917311124331</v>
+        <v>2561.111111111111</v>
       </c>
       <c r="D5" t="n">
-        <v>15.27312302007908</v>
+        <v>298.1895446777344</v>
       </c>
       <c r="E5" t="n">
-        <v>11.1596644651599</v>
+        <v>217.8791633674076</v>
       </c>
       <c r="F5" t="n">
         <v>1.368600558534824</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3619540668042467</v>
+        <v>0.3619540668042466</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>1.439024390243902</v>
+        <v>3.642113095238095</v>
       </c>
       <c r="J5" t="n">
-        <v>1.439024390243902</v>
+        <v>28.09523809523809</v>
       </c>
       <c r="K5" t="n">
-        <v>1.439024390243902</v>
-      </c>
-      <c r="N5" t="inlineStr">
+        <v>11.00213913690476</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>28.09523809523809</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O5" t="n">
+        <v>6.398809523809524</v>
+      </c>
+      <c r="P5" t="n">
+        <v>5.872395833333333</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.642113095238095</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="Y5" s="2" t="n">
         <v>1.193435133598582</v>
       </c>
     </row>
@@ -694,17 +840,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6.712671029149316</v>
+        <v>2558.730158730159</v>
       </c>
       <c r="D6" t="n">
-        <v>15.16964402140641</v>
+        <v>296.1692404179346</v>
       </c>
       <c r="E6" t="n">
-        <v>11.2429380009814</v>
+        <v>219.5049800191607</v>
       </c>
       <c r="F6" t="n">
         <v>1.349259777122514</v>
@@ -713,23 +859,47 @@
         <v>0.3665679147414566</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>1.407298018292683</v>
+        <v>4.073660714285714</v>
       </c>
       <c r="J6" t="n">
-        <v>1.407298018292683</v>
+        <v>27.47581845238095</v>
       </c>
       <c r="K6" t="n">
-        <v>1.407298018292683</v>
-      </c>
-      <c r="N6" t="inlineStr">
+        <v>11.00539434523809</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>27.47581845238095</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3</v>
+      </c>
+      <c r="O6" t="n">
+        <v>6.441592261904762</v>
+      </c>
+      <c r="P6" t="n">
+        <v>6.030505952380952</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4.073660714285714</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="Y6" s="2" t="n">
         <v>0.5297107325592462</v>
       </c>
     </row>
@@ -741,43 +911,67 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6.694527067221892</v>
+        <v>2551.814058956916</v>
       </c>
       <c r="D7" t="n">
-        <v>15.04595944358081</v>
+        <v>293.7544462794349</v>
       </c>
       <c r="E7" t="n">
-        <v>11.28334905752322</v>
+        <v>220.293957789739</v>
       </c>
       <c r="F7" t="n">
         <v>1.333465743803154</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3716122246085408</v>
+        <v>0.3716122246085409</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>1.365853658536585</v>
+        <v>3.809523809523809</v>
       </c>
       <c r="J7" t="n">
-        <v>1.365853658536585</v>
+        <v>26.66666666666666</v>
       </c>
       <c r="K7" t="n">
-        <v>1.365853658536585</v>
-      </c>
-      <c r="N7" t="inlineStr">
+        <v>10.74404761904762</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>26.66666666666666</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>6.65922619047619</v>
+      </c>
+      <c r="P7" t="n">
+        <v>5.840773809523809</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>0.8</v>
+      <c r="Y7" s="2" t="n">
+        <v>3.65</v>
       </c>
     </row>
     <row r="8">
@@ -788,43 +982,67 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6.708209399167163</v>
+        <v>2557.02947845805</v>
       </c>
       <c r="D8" t="n">
-        <v>14.55468783727506</v>
+        <v>284.1629530134655</v>
       </c>
       <c r="E8" t="n">
-        <v>11.27497964079787</v>
+        <v>220.130554891768</v>
       </c>
       <c r="F8" t="n">
         <v>1.290883735577646</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3979336671926523</v>
+        <v>0.3979336671926524</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>1.277248475609756</v>
+        <v>3.809523809523809</v>
       </c>
       <c r="J8" t="n">
-        <v>1.277248475609756</v>
+        <v>24.93675595238095</v>
       </c>
       <c r="K8" t="n">
-        <v>1.277248475609756</v>
-      </c>
-      <c r="N8" t="inlineStr">
+        <v>10.27576264880952</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>24.93675595238095</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3</v>
+      </c>
+      <c r="O8" t="n">
+        <v>6.612723214285714</v>
+      </c>
+      <c r="P8" t="n">
+        <v>5.744047619047619</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>1.043593988185976</v>
+      <c r="Y8" s="2" t="n">
+        <v>3.061011904761904</v>
       </c>
     </row>
     <row r="9">
@@ -835,17 +1053,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6.608566329565735</v>
+        <v>2519.047619047619</v>
       </c>
       <c r="D9" t="n">
-        <v>13.57806273204524</v>
+        <v>265.0955104827881</v>
       </c>
       <c r="E9" t="n">
-        <v>11.30355460469316</v>
+        <v>220.6884470440093</v>
       </c>
       <c r="F9" t="n">
         <v>1.201220607755345</v>
@@ -854,24 +1072,48 @@
         <v>0.4504447149197535</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>1.09984756097561</v>
+        <v>3.809523809523809</v>
       </c>
       <c r="J9" t="n">
-        <v>1.09984756097561</v>
+        <v>21.47321428571428</v>
       </c>
       <c r="K9" t="n">
-        <v>1.09984756097561</v>
-      </c>
-      <c r="N9" t="inlineStr">
+        <v>9.65727306547619</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>21.47321428571428</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3</v>
+      </c>
+      <c r="O9" t="n">
+        <v>7.213541666666666</v>
+      </c>
+      <c r="P9" t="n">
+        <v>6.1328125</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>1.043593988185976</v>
+      <c r="Y9" s="2" t="n">
+        <v>17.87490699404762</v>
       </c>
     </row>
     <row r="10">
@@ -882,17 +1124,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6.549672813801309</v>
+        <v>2496.598639455782</v>
       </c>
       <c r="D10" t="n">
-        <v>13.37110466491885</v>
+        <v>261.0549006007967</v>
       </c>
       <c r="E10" t="n">
-        <v>11.3178420968172</v>
+        <v>220.967393318812</v>
       </c>
       <c r="F10" t="n">
         <v>1.181418202386749</v>
@@ -901,24 +1143,48 @@
         <v>0.4603571501246703</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>1.04735137195122</v>
+        <v>4.285714285714286</v>
       </c>
       <c r="J10" t="n">
-        <v>1.04735137195122</v>
+        <v>20.44828869047619</v>
       </c>
       <c r="K10" t="n">
-        <v>1.04735137195122</v>
-      </c>
-      <c r="N10" t="inlineStr">
+        <v>9.663318452380953</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>20.44828869047619</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3</v>
+      </c>
+      <c r="O10" t="n">
+        <v>7.641369047619047</v>
+      </c>
+      <c r="P10" t="n">
+        <v>6.277901785714286</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>1.043593988185976</v>
+      <c r="Y10" s="2" t="n">
+        <v>8.176618303571427</v>
       </c>
     </row>
     <row r="11">
@@ -929,35 +1195,67 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6.526472337894111</v>
+        <v>2487.755102040816</v>
       </c>
       <c r="D11" t="n">
-        <v>12.73002486403396</v>
+        <v>248.5385806787582</v>
       </c>
       <c r="E11" t="n">
-        <v>11.25722544658475</v>
+        <v>219.7839253857022</v>
       </c>
       <c r="F11" t="n">
-        <v>1.130831475698662</v>
+        <v>1.130831475698661</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5060924539216437</v>
+        <v>0.5060924539216436</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7206554878048781</v>
+        <v>4.285714285714286</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7206554878048781</v>
+        <v>14.06994047619048</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7206554878048781</v>
+        <v>8.286365327380953</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>14.06994047619048</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>7.706473214285714</v>
+      </c>
+      <c r="P11" t="n">
+        <v>7.083333333333333</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="n">
+        <v>0.85</v>
       </c>
     </row>
     <row r="12">
@@ -968,35 +1266,67 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.505056513979774</v>
+        <v>2479.591836734694</v>
       </c>
       <c r="D12" t="n">
-        <v>12.57531400424678</v>
+        <v>245.5180353210086</v>
       </c>
       <c r="E12" t="n">
-        <v>11.21436305743892</v>
+        <v>218.9470882642837</v>
       </c>
       <c r="F12" t="n">
         <v>1.121357846168989</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5169199119247562</v>
+        <v>0.5169199119247561</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7089367378048781</v>
+        <v>3.809523809523809</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7089367378048781</v>
+        <v>13.84114583333333</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7089367378048781</v>
+        <v>8.141276041666666</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>13.84114583333333</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O12" t="n">
+        <v>7.637648809523809</v>
+      </c>
+      <c r="P12" t="n">
+        <v>7.276785714285714</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="n">
+        <v>19.71004026610644</v>
       </c>
     </row>
     <row r="13">
@@ -1007,35 +1337,67 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6.555026769779893</v>
+        <v>2498.639455782313</v>
       </c>
       <c r="D13" t="n">
-        <v>12.83451926708221</v>
+        <v>250.5787095001766</v>
       </c>
       <c r="E13" t="n">
-        <v>11.02515913509741</v>
+        <v>215.2531069233304</v>
       </c>
       <c r="F13" t="n">
         <v>1.164111928890432</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5000634595529334</v>
+        <v>0.5000634595529333</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7069359756097561</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7069359756097561</v>
+        <v>13.80208333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7069359756097561</v>
+        <v>7.931547619047618</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>13.80208333333333</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>7.36235119047619</v>
+      </c>
+      <c r="P13" t="n">
+        <v>7.228422619047619</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="n">
+        <v>2.4</v>
       </c>
     </row>
     <row r="14">
@@ -1046,35 +1408,67 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6.790898274836407</v>
+        <v>2588.548752834467</v>
       </c>
       <c r="D14" t="n">
-        <v>12.02097444127246</v>
+        <v>234.695215281986</v>
       </c>
       <c r="E14" t="n">
-        <v>10.84085795356006</v>
+        <v>211.6548457599822</v>
       </c>
       <c r="F14" t="n">
         <v>1.108858218857563</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5905514516983307</v>
+        <v>0.5905514516983308</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6876905487804879</v>
+        <v>2.036830357142857</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6876905487804879</v>
+        <v>13.42633928571428</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6876905487804879</v>
+        <v>6.728515624999999</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>13.42633928571428</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2</v>
+      </c>
+      <c r="O14" t="n">
+        <v>7.165178571428571</v>
+      </c>
+      <c r="P14" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.036830357142857</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="n">
+        <v>6.351283482142857</v>
       </c>
     </row>
     <row r="15">
@@ -1085,35 +1479,67 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6.924747174301012</v>
+        <v>2639.569160997732</v>
       </c>
       <c r="D15" t="n">
-        <v>11.53807224878451</v>
+        <v>225.2671248572213</v>
       </c>
       <c r="E15" t="n">
-        <v>10.54124158475457</v>
+        <v>205.8051928452083</v>
       </c>
       <c r="F15" t="n">
         <v>1.094564824837296</v>
       </c>
       <c r="G15" t="n">
-        <v>0.653653028348183</v>
+        <v>0.6536530283481828</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7094131097560976</v>
+        <v>1.147693452380952</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7094131097560976</v>
+        <v>13.85044642857143</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7094131097560976</v>
+        <v>5.08975074404762</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>13.85044642857143</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.610491071428571</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.750372023809524</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.147693452380952</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="n">
+        <v>5.803920200892857</v>
       </c>
     </row>
     <row r="16">
@@ -1124,35 +1550,64 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6.901844140392623</v>
+        <v>2630.839002267574</v>
       </c>
       <c r="D16" t="n">
-        <v>11.27988235834168</v>
+        <v>220.2262746152423</v>
       </c>
       <c r="E16" t="n">
-        <v>10.39490013006257</v>
+        <v>202.9480501583644</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0851361934416</v>
+        <v>1.085136193441599</v>
       </c>
       <c r="G16" t="n">
         <v>0.6816569565161984</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6576791158536586</v>
+        <v>1.026785714285714</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6576791158536586</v>
+        <v>12.84040178571428</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6576791158536586</v>
+        <v>5.892237103174604</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>12.84040178571428</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.026785714285714</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="n">
+        <v>3.842075892857142</v>
       </c>
     </row>
     <row r="17">
@@ -1163,17 +1618,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6.805770374776919</v>
+        <v>2594.21768707483</v>
       </c>
       <c r="D17" t="n">
-        <v>11.08721174263373</v>
+        <v>216.4646102133251</v>
       </c>
       <c r="E17" t="n">
-        <v>10.24264062032467</v>
+        <v>199.9753644920531</v>
       </c>
       <c r="F17" t="n">
         <v>1.082456385381047</v>
@@ -1182,16 +1637,42 @@
         <v>0.6957327905811944</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5983231707317074</v>
+        <v>3.809523809523809</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5983231707317074</v>
+        <v>11.68154761904762</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5983231707317074</v>
+        <v>7.745535714285714</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>11.68154761904762</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="18">
@@ -1202,26 +1683,61 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6.676977989292088</v>
+        <v>2545.124716553288</v>
       </c>
       <c r="D18" t="n">
-        <v>10.723091439503</v>
+        <v>209.3555947712489</v>
       </c>
       <c r="E18" t="n">
-        <v>10.12242273877307</v>
+        <v>197.6282534712837</v>
       </c>
       <c r="F18" t="n">
         <v>1.059340408539659</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7297091463464476</v>
+        <v>0.7297091463464477</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="J18" t="n">
+        <v>9.071800595238095</v>
+      </c>
+      <c r="K18" t="n">
+        <v>6.67875744047619</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>9.071800595238095</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="n">
+        <v>1.273561507936508</v>
       </c>
     </row>
     <row r="19">
@@ -1232,26 +1748,64 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6.486317668054729</v>
+        <v>2472.448979591837</v>
       </c>
       <c r="D19" t="n">
-        <v>10.43632661424032</v>
+        <v>203.756852944692</v>
       </c>
       <c r="E19" t="n">
-        <v>9.996286839973637</v>
+        <v>195.1656002090091</v>
       </c>
       <c r="F19" t="n">
         <v>1.044020322876994</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7483637696400907</v>
+        <v>0.7483637696400909</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.8909970238095237</v>
+      </c>
+      <c r="J19" t="n">
+        <v>7.607886904761904</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.261532738095238</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2</v>
+      </c>
+      <c r="O19" t="n">
+        <v>7.607886904761904</v>
+      </c>
+      <c r="P19" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.8909970238095237</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="n">
+        <v>1.07328869047619</v>
       </c>
     </row>
     <row r="20">
@@ -1262,17 +1816,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6.270969660916122</v>
+        <v>2390.362811791383</v>
       </c>
       <c r="D20" t="n">
-        <v>10.21262968168026</v>
+        <v>199.3894366423289</v>
       </c>
       <c r="E20" t="n">
-        <v>9.766671861090311</v>
+        <v>190.6826410974775</v>
       </c>
       <c r="F20" t="n">
         <v>1.045661186014308</v>
@@ -1281,6 +1835,44 @@
         <v>0.7555607604497294</v>
       </c>
       <c r="H20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.9188988095238094</v>
+      </c>
+      <c r="J20" t="n">
+        <v>7.144717261904762</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.275173611111112</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2</v>
+      </c>
+      <c r="O20" t="n">
+        <v>7.144717261904762</v>
+      </c>
+      <c r="P20" t="n">
+        <v>4.761904761904762</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.9188988095238094</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1292,25 +1884,58 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6.151695419393219</v>
+        <v>2344.897959183673</v>
       </c>
       <c r="D21" t="n">
-        <v>10.20671162663437</v>
+        <v>199.2738936628614</v>
       </c>
       <c r="E21" t="n">
-        <v>9.697685829023037</v>
+        <v>189.3357709475926</v>
       </c>
       <c r="F21" t="n">
         <v>1.052489408977132</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7420497093841035</v>
+        <v>0.7420497093841036</v>
       </c>
       <c r="H21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.9988839285714285</v>
+      </c>
+      <c r="J21" t="n">
+        <v>7.67485119047619</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.49423363095238</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2</v>
+      </c>
+      <c r="O21" t="n">
+        <v>7.67485119047619</v>
+      </c>
+      <c r="P21" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.017485119047619</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.9988839285714285</v>
+      </c>
+      <c r="U21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1321,7 +1946,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
       </c>
     </row>
     <row r="23">
@@ -1344,6 +1969,38 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/measurements/26/Filled_2D_sections/axial/week26_axial_Batch_Allmarks.xlsx
+++ b/measurements/26/Filled_2D_sections/axial/week26_axial_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2006,4 +2212,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week26_axial_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>axial</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2525.272108843537</v>
+      </c>
+      <c r="D10" t="n">
+        <v>71.33787625756149</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2344.897959183673</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2639.569160997732</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>252.4611842206546</v>
+      </c>
+      <c r="D11" t="n">
+        <v>37.58817963384354</v>
+      </c>
+      <c r="E11" t="n">
+        <v>199.2738936628614</v>
+      </c>
+      <c r="F11" t="n">
+        <v>299.9110802582332</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.193435133598582</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.1312604776776387</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.044020322876994</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.389084981592187</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.5297107325592462</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.1547508316173418</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.3534481258339988</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.7555607604497294</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis2_s00_idx0104.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis2_s01_idx0105.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis2_s02_idx0107.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis2_s03_idx0109.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis2_s04_idx0111.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis2_s05_idx0113.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>4</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis2_s06_idx0115.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis2_s07_idx0117.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis2_s08_idx0119.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>4</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis2_s09_idx0121.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis2_s10_idx0122.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>4</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis2_s11_idx0124.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis2_s12_idx0126.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>4</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis2_s13_idx0128.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>4</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis2_s14_idx0130.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>3</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis2_s15_idx0132.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis2_s16_idx0134.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis2_s17_idx0136.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis2_s18_idx0138.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis2_s19_idx0139.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>4</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>4</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.6708203932499369</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.3663475485325233</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.8207826816681233</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.6805570473787207</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>17</v>
+      </c>
+      <c r="C48" t="n">
+        <v>19.71004026610644</v>
+      </c>
+      <c r="D48" t="n">
+        <v>7.098222599284863</v>
+      </c>
+      <c r="E48" t="n">
+        <v>9.071800595238095</v>
+      </c>
+      <c r="F48" t="n">
+        <v>28.13802083333333</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>48</v>
+      </c>
+      <c r="C49" t="n">
+        <v>5.541527157738095</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.463818346778222</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="F49" t="n">
+        <v>7.706473214285714</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>8</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1.223493303571428</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.4275809308462469</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.8909970238095237</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2.036830357142857</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>